--- a/activity/M01A01/M01A01_Parametros.xlsx
+++ b/activity/M01A01/M01A01_Parametros.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29131"/>
   <workbookPr updateLinks="never" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEC85501-2A72-4458-9230-154F41F5C11D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA022F2A-5C7F-4563-89D2-6FF263312DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="773" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -165,7 +165,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="86">
   <si>
     <t>Unidad</t>
   </si>
@@ -384,9 +384,6 @@
   </si>
   <si>
     <t>M01A01</t>
-  </si>
-  <si>
-    <t>https://github.com/rcfdtools/R.HCMC/blob/main/activity/M01A01/Readme.md</t>
   </si>
   <si>
     <t>Calificación</t>
@@ -435,7 +432,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -529,6 +526,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0070C0"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -900,7 +903,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1177,12 +1180,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1201,38 +1210,38 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="22" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3035,23 +3044,23 @@
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="B2" s="92" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92"/>
-      <c r="O2" s="92"/>
-      <c r="P2" s="92"/>
+      <c r="B2" s="91" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="91"/>
+      <c r="N2" s="91"/>
+      <c r="O2" s="91"/>
+      <c r="P2" s="91"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.45">
       <c r="B3" s="65" t="s">
@@ -3120,31 +3129,31 @@
         <v>59</v>
       </c>
       <c r="H4" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="I4" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="J4" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="J4" s="28" t="s">
+      <c r="K4" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="K4" s="28" t="s">
+      <c r="L4" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="L4" s="28" t="s">
+      <c r="M4" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="M4" s="28" t="s">
+      <c r="N4" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="N4" s="28" t="s">
+      <c r="O4" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="O4" s="28" t="s">
+      <c r="P4" s="32" t="s">
         <v>82</v>
-      </c>
-      <c r="P4" s="32" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:19" s="11" customFormat="1" x14ac:dyDescent="0.45">
@@ -3534,40 +3543,41 @@
       </c>
     </row>
     <row r="12" spans="1:19" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="91" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="91"/>
-      <c r="D12" s="91"/>
-      <c r="E12" s="91"/>
-      <c r="F12" s="91"/>
-      <c r="G12" s="91"/>
-      <c r="H12" s="91"/>
-      <c r="I12" s="91"/>
-      <c r="J12" s="91"/>
-      <c r="K12" s="91"/>
-      <c r="L12" s="91"/>
-      <c r="M12" s="91"/>
-      <c r="N12" s="91"/>
-      <c r="O12" s="91"/>
-      <c r="P12" s="91"/>
+      <c r="B12" s="109" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",P1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",P1," en GitHub."))</f>
+        <v>Ir a actividad M01A01 en GitHub.</v>
+      </c>
+      <c r="C12" s="109"/>
+      <c r="D12" s="109"/>
+      <c r="E12" s="109"/>
+      <c r="F12" s="109"/>
+      <c r="G12" s="110"/>
+      <c r="H12" s="110"/>
+      <c r="I12" s="110"/>
+      <c r="J12" s="110"/>
+      <c r="K12" s="110"/>
+      <c r="L12" s="110"/>
+      <c r="M12" s="110"/>
+      <c r="N12" s="110"/>
+      <c r="O12" s="110"/>
+      <c r="P12" s="110"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="B13" s="91"/>
-      <c r="C13" s="91"/>
-      <c r="D13" s="91"/>
-      <c r="E13" s="91"/>
-      <c r="F13" s="91"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="91"/>
-      <c r="J13" s="91"/>
-      <c r="K13" s="91"/>
-      <c r="L13" s="91"/>
-      <c r="M13" s="91"/>
-      <c r="N13" s="91"/>
-      <c r="O13" s="91"/>
-      <c r="P13" s="91"/>
+      <c r="B13" s="109"/>
+      <c r="C13" s="109"/>
+      <c r="D13" s="109"/>
+      <c r="E13" s="109"/>
+      <c r="F13" s="109"/>
+      <c r="G13" s="111"/>
+      <c r="H13" s="111"/>
+      <c r="I13" s="111"/>
+      <c r="J13" s="111"/>
+      <c r="K13" s="111"/>
+      <c r="L13" s="111"/>
+      <c r="M13" s="111"/>
+      <c r="N13" s="111"/>
+      <c r="O13" s="111"/>
+      <c r="P13" s="111"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B18" s="13"/>
@@ -3604,17 +3614,14 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B12:P12"/>
     <mergeCell ref="B2:P2"/>
-    <mergeCell ref="B13:P13"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="B12" r:id="rId1" xr:uid="{7AC7C1A8-5742-4C6D-BC77-BBAC6D9A9582}"/>
-  </hyperlinks>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-  <drawing r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3721,90 +3728,90 @@
       <c r="E2" s="10"/>
       <c r="F2" s="10"/>
       <c r="G2" s="47"/>
-      <c r="H2" s="99" t="str">
+      <c r="H2" s="92" t="str">
         <f>Calificacion!C$4</f>
         <v>Grupo 1</v>
       </c>
-      <c r="I2" s="100"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="99" t="str">
+      <c r="I2" s="93"/>
+      <c r="J2" s="94"/>
+      <c r="K2" s="92" t="str">
         <f>Calificacion!D$4</f>
         <v>Grupo 2</v>
       </c>
-      <c r="L2" s="100"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="99" t="str">
+      <c r="L2" s="93"/>
+      <c r="M2" s="94"/>
+      <c r="N2" s="92" t="str">
         <f>Calificacion!E$4</f>
         <v>Grupo 3</v>
       </c>
-      <c r="O2" s="100"/>
-      <c r="P2" s="101"/>
-      <c r="Q2" s="99" t="str">
+      <c r="O2" s="93"/>
+      <c r="P2" s="94"/>
+      <c r="Q2" s="92" t="str">
         <f>Calificacion!F$4</f>
         <v>Grupo 4</v>
       </c>
-      <c r="R2" s="100"/>
-      <c r="S2" s="101"/>
-      <c r="T2" s="99" t="str">
+      <c r="R2" s="93"/>
+      <c r="S2" s="94"/>
+      <c r="T2" s="92" t="str">
         <f>Calificacion!G$4</f>
         <v>Grupo 5</v>
       </c>
-      <c r="U2" s="100"/>
-      <c r="V2" s="101"/>
-      <c r="W2" s="99" t="str">
+      <c r="U2" s="93"/>
+      <c r="V2" s="94"/>
+      <c r="W2" s="92" t="str">
         <f>Calificacion!H$4</f>
         <v>Grupo 6</v>
       </c>
-      <c r="X2" s="100"/>
-      <c r="Y2" s="101"/>
-      <c r="Z2" s="99" t="str">
+      <c r="X2" s="93"/>
+      <c r="Y2" s="94"/>
+      <c r="Z2" s="92" t="str">
         <f>Calificacion!I$4</f>
         <v>Grupo 7</v>
       </c>
-      <c r="AA2" s="100"/>
-      <c r="AB2" s="101"/>
-      <c r="AC2" s="99" t="str">
+      <c r="AA2" s="93"/>
+      <c r="AB2" s="94"/>
+      <c r="AC2" s="92" t="str">
         <f>Calificacion!J$4</f>
         <v>Grupo 8</v>
       </c>
-      <c r="AD2" s="100"/>
-      <c r="AE2" s="101"/>
-      <c r="AF2" s="99" t="str">
+      <c r="AD2" s="93"/>
+      <c r="AE2" s="94"/>
+      <c r="AF2" s="92" t="str">
         <f>Calificacion!K$4</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AG2" s="100"/>
-      <c r="AH2" s="101"/>
-      <c r="AI2" s="99" t="str">
+      <c r="AG2" s="93"/>
+      <c r="AH2" s="94"/>
+      <c r="AI2" s="92" t="str">
         <f>Calificacion!L$4</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AJ2" s="100"/>
-      <c r="AK2" s="101"/>
-      <c r="AL2" s="99" t="str">
+      <c r="AJ2" s="93"/>
+      <c r="AK2" s="94"/>
+      <c r="AL2" s="92" t="str">
         <f>Calificacion!M$4</f>
         <v>Grupo 11</v>
       </c>
-      <c r="AM2" s="100"/>
-      <c r="AN2" s="101"/>
-      <c r="AO2" s="99" t="str">
+      <c r="AM2" s="93"/>
+      <c r="AN2" s="94"/>
+      <c r="AO2" s="92" t="str">
         <f>Calificacion!N$4</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AP2" s="100"/>
-      <c r="AQ2" s="101"/>
-      <c r="AR2" s="99" t="str">
+      <c r="AP2" s="93"/>
+      <c r="AQ2" s="94"/>
+      <c r="AR2" s="92" t="str">
         <f>Calificacion!O$4</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AS2" s="100"/>
-      <c r="AT2" s="101"/>
-      <c r="AU2" s="99" t="str">
+      <c r="AS2" s="93"/>
+      <c r="AT2" s="94"/>
+      <c r="AU2" s="92" t="str">
         <f>Calificacion!P$4</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AV2" s="100"/>
-      <c r="AW2" s="101"/>
+      <c r="AV2" s="93"/>
+      <c r="AW2" s="94"/>
     </row>
     <row r="3" spans="1:49" x14ac:dyDescent="0.45">
       <c r="B3" s="33" t="s">
@@ -3953,7 +3960,7 @@
       </c>
     </row>
     <row r="4" spans="1:49" x14ac:dyDescent="0.45">
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="96" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="41" t="s">
@@ -4043,7 +4050,7 @@
       <c r="AW4" s="76"/>
     </row>
     <row r="5" spans="1:49" x14ac:dyDescent="0.45">
-      <c r="B5" s="95"/>
+      <c r="B5" s="97"/>
       <c r="C5" s="3" t="s">
         <v>34</v>
       </c>
@@ -4103,7 +4110,7 @@
       <c r="AW5" s="79"/>
     </row>
     <row r="6" spans="1:49" ht="33" x14ac:dyDescent="0.45">
-      <c r="B6" s="95"/>
+      <c r="B6" s="97"/>
       <c r="C6" s="3" t="s">
         <v>35</v>
       </c>
@@ -4163,7 +4170,7 @@
       <c r="AW6" s="79"/>
     </row>
     <row r="7" spans="1:49" x14ac:dyDescent="0.45">
-      <c r="B7" s="95"/>
+      <c r="B7" s="97"/>
       <c r="C7" s="3" t="s">
         <v>36</v>
       </c>
@@ -4223,7 +4230,7 @@
       <c r="AW7" s="79"/>
     </row>
     <row r="8" spans="1:49" ht="33" x14ac:dyDescent="0.45">
-      <c r="B8" s="96"/>
+      <c r="B8" s="98"/>
       <c r="C8" s="6" t="s">
         <v>37</v>
       </c>
@@ -4283,7 +4290,7 @@
       <c r="AW8" s="82"/>
     </row>
     <row r="9" spans="1:49" x14ac:dyDescent="0.45">
-      <c r="B9" s="97" t="s">
+      <c r="B9" s="99" t="s">
         <v>42</v>
       </c>
       <c r="C9" s="38" t="s">
@@ -4345,7 +4352,7 @@
       <c r="AW9" s="85"/>
     </row>
     <row r="10" spans="1:49" x14ac:dyDescent="0.45">
-      <c r="B10" s="95"/>
+      <c r="B10" s="97"/>
       <c r="C10" s="3" t="s">
         <v>14</v>
       </c>
@@ -4405,7 +4412,7 @@
       <c r="AW10" s="79"/>
     </row>
     <row r="11" spans="1:49" x14ac:dyDescent="0.45">
-      <c r="B11" s="95"/>
+      <c r="B11" s="97"/>
       <c r="C11" s="3" t="s">
         <v>15</v>
       </c>
@@ -4465,7 +4472,7 @@
       <c r="AW11" s="79"/>
     </row>
     <row r="12" spans="1:49" x14ac:dyDescent="0.45">
-      <c r="B12" s="95"/>
+      <c r="B12" s="97"/>
       <c r="C12" s="3" t="s">
         <v>16</v>
       </c>
@@ -4525,7 +4532,7 @@
       <c r="AW12" s="79"/>
     </row>
     <row r="13" spans="1:49" x14ac:dyDescent="0.45">
-      <c r="B13" s="95"/>
+      <c r="B13" s="97"/>
       <c r="C13" s="3" t="s">
         <v>17</v>
       </c>
@@ -4585,7 +4592,7 @@
       <c r="AW13" s="79"/>
     </row>
     <row r="14" spans="1:49" x14ac:dyDescent="0.45">
-      <c r="B14" s="95"/>
+      <c r="B14" s="97"/>
       <c r="C14" s="3" t="s">
         <v>18</v>
       </c>
@@ -4645,7 +4652,7 @@
       <c r="AW14" s="79"/>
     </row>
     <row r="15" spans="1:49" x14ac:dyDescent="0.45">
-      <c r="B15" s="95"/>
+      <c r="B15" s="97"/>
       <c r="C15" s="3" t="s">
         <v>19</v>
       </c>
@@ -4703,7 +4710,7 @@
       <c r="AW15" s="79"/>
     </row>
     <row r="16" spans="1:49" ht="33" x14ac:dyDescent="0.45">
-      <c r="B16" s="95"/>
+      <c r="B16" s="97"/>
       <c r="C16" s="3" t="s">
         <v>40</v>
       </c>
@@ -4761,7 +4768,7 @@
       <c r="AW16" s="79"/>
     </row>
     <row r="17" spans="2:49" ht="33" x14ac:dyDescent="0.45">
-      <c r="B17" s="95"/>
+      <c r="B17" s="97"/>
       <c r="C17" s="3" t="s">
         <v>41</v>
       </c>
@@ -4819,7 +4826,7 @@
       <c r="AW17" s="79"/>
     </row>
     <row r="18" spans="2:49" x14ac:dyDescent="0.45">
-      <c r="B18" s="98"/>
+      <c r="B18" s="100"/>
       <c r="C18" s="58" t="s">
         <v>70</v>
       </c>
@@ -4873,7 +4880,7 @@
       <c r="AW18" s="88"/>
     </row>
     <row r="19" spans="2:49" x14ac:dyDescent="0.45">
-      <c r="B19" s="96"/>
+      <c r="B19" s="98"/>
       <c r="C19" s="6"/>
       <c r="D19" s="7"/>
       <c r="E19" s="8"/>
@@ -4923,98 +4930,98 @@
       <c r="AW19" s="82"/>
     </row>
     <row r="20" spans="2:49" ht="17.2" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="102" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="102"/>
-      <c r="D20" s="102"/>
-      <c r="E20" s="102"/>
-      <c r="F20" s="102"/>
-      <c r="G20" s="102"/>
-      <c r="H20" s="93">
+      <c r="B20" s="101" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="101"/>
+      <c r="D20" s="101"/>
+      <c r="E20" s="101"/>
+      <c r="F20" s="101"/>
+      <c r="G20" s="101"/>
+      <c r="H20" s="95">
         <f>AVERAGE(H4:H19)</f>
         <v>0</v>
       </c>
-      <c r="I20" s="93"/>
-      <c r="J20" s="93"/>
-      <c r="K20" s="93">
+      <c r="I20" s="95"/>
+      <c r="J20" s="95"/>
+      <c r="K20" s="95">
         <f>AVERAGE(K4:K19)</f>
         <v>0</v>
       </c>
-      <c r="L20" s="93"/>
-      <c r="M20" s="93"/>
-      <c r="N20" s="93">
+      <c r="L20" s="95"/>
+      <c r="M20" s="95"/>
+      <c r="N20" s="95">
         <f>AVERAGE(N4:N19)</f>
         <v>0</v>
       </c>
-      <c r="O20" s="93"/>
-      <c r="P20" s="93"/>
-      <c r="Q20" s="93">
+      <c r="O20" s="95"/>
+      <c r="P20" s="95"/>
+      <c r="Q20" s="95">
         <f>AVERAGE(Q4:Q19)</f>
         <v>0</v>
       </c>
-      <c r="R20" s="93"/>
-      <c r="S20" s="93"/>
-      <c r="T20" s="93">
+      <c r="R20" s="95"/>
+      <c r="S20" s="95"/>
+      <c r="T20" s="95">
         <f>AVERAGE(T4:T19)</f>
         <v>0</v>
       </c>
-      <c r="U20" s="93"/>
-      <c r="V20" s="93"/>
-      <c r="W20" s="93">
+      <c r="U20" s="95"/>
+      <c r="V20" s="95"/>
+      <c r="W20" s="95">
         <f>AVERAGE(W4:W19)</f>
         <v>0</v>
       </c>
-      <c r="X20" s="93"/>
-      <c r="Y20" s="93"/>
-      <c r="Z20" s="93">
+      <c r="X20" s="95"/>
+      <c r="Y20" s="95"/>
+      <c r="Z20" s="95">
         <f>AVERAGE(Z4:Z19)</f>
         <v>0</v>
       </c>
-      <c r="AA20" s="93"/>
-      <c r="AB20" s="93"/>
-      <c r="AC20" s="93">
+      <c r="AA20" s="95"/>
+      <c r="AB20" s="95"/>
+      <c r="AC20" s="95">
         <f>AVERAGE(AC4:AC19)</f>
         <v>0</v>
       </c>
-      <c r="AD20" s="93"/>
-      <c r="AE20" s="93"/>
-      <c r="AF20" s="93">
+      <c r="AD20" s="95"/>
+      <c r="AE20" s="95"/>
+      <c r="AF20" s="95">
         <f>AVERAGE(AF4:AF19)</f>
         <v>0</v>
       </c>
-      <c r="AG20" s="93"/>
-      <c r="AH20" s="93"/>
-      <c r="AI20" s="93">
+      <c r="AG20" s="95"/>
+      <c r="AH20" s="95"/>
+      <c r="AI20" s="95">
         <f>AVERAGE(AI4:AI19)</f>
         <v>0</v>
       </c>
-      <c r="AJ20" s="93"/>
-      <c r="AK20" s="93"/>
-      <c r="AL20" s="93">
+      <c r="AJ20" s="95"/>
+      <c r="AK20" s="95"/>
+      <c r="AL20" s="95">
         <f>AVERAGE(AL4:AL19)</f>
         <v>0</v>
       </c>
-      <c r="AM20" s="93"/>
-      <c r="AN20" s="93"/>
-      <c r="AO20" s="93">
+      <c r="AM20" s="95"/>
+      <c r="AN20" s="95"/>
+      <c r="AO20" s="95">
         <f>AVERAGE(AO4:AO19)</f>
         <v>0</v>
       </c>
-      <c r="AP20" s="93"/>
-      <c r="AQ20" s="93"/>
-      <c r="AR20" s="93">
+      <c r="AP20" s="95"/>
+      <c r="AQ20" s="95"/>
+      <c r="AR20" s="95">
         <f>AVERAGE(AR4:AR19)</f>
         <v>0</v>
       </c>
-      <c r="AS20" s="93"/>
-      <c r="AT20" s="93"/>
-      <c r="AU20" s="93">
+      <c r="AS20" s="95"/>
+      <c r="AT20" s="95"/>
+      <c r="AU20" s="95">
         <f>AVERAGE(AU4:AU19)</f>
         <v>0</v>
       </c>
-      <c r="AV20" s="93"/>
-      <c r="AW20" s="93"/>
+      <c r="AV20" s="95"/>
+      <c r="AW20" s="95"/>
     </row>
     <row r="21" spans="2:49" ht="17.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B21" s="1" t="s">
@@ -5390,6 +5397,23 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="Q20:S20"/>
+    <mergeCell ref="T20:V20"/>
+    <mergeCell ref="W20:Y20"/>
+    <mergeCell ref="Z20:AB20"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="B9:B19"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="Z2:AB2"/>
     <mergeCell ref="AU2:AW2"/>
     <mergeCell ref="AR2:AT2"/>
     <mergeCell ref="AR20:AT20"/>
@@ -5404,23 +5428,6 @@
     <mergeCell ref="AI20:AK20"/>
     <mergeCell ref="AL20:AN20"/>
     <mergeCell ref="AO20:AQ20"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="T2:V2"/>
-    <mergeCell ref="W2:Y2"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="B9:B19"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="Q20:S20"/>
-    <mergeCell ref="T20:V20"/>
-    <mergeCell ref="W20:Y20"/>
-    <mergeCell ref="Z20:AB20"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5537,72 +5544,72 @@
         <f>Calificacion!C$4</f>
         <v>Grupo 1</v>
       </c>
-      <c r="E2" s="106"/>
+      <c r="E2" s="103"/>
       <c r="F2" s="105" t="str">
         <f>Calificacion!D$4</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="106"/>
+      <c r="G2" s="103"/>
       <c r="H2" s="105" t="str">
         <f>Calificacion!E$4</f>
         <v>Grupo 3</v>
       </c>
-      <c r="I2" s="106"/>
+      <c r="I2" s="103"/>
       <c r="J2" s="105" t="str">
         <f>Calificacion!F$4</f>
         <v>Grupo 4</v>
       </c>
-      <c r="K2" s="106"/>
+      <c r="K2" s="103"/>
       <c r="L2" s="105" t="str">
         <f>Calificacion!G$4</f>
         <v>Grupo 5</v>
       </c>
-      <c r="M2" s="106"/>
+      <c r="M2" s="103"/>
       <c r="N2" s="105" t="str">
         <f>Calificacion!H$4</f>
         <v>Grupo 6</v>
       </c>
-      <c r="O2" s="106"/>
+      <c r="O2" s="103"/>
       <c r="P2" s="105" t="str">
         <f>Calificacion!I$4</f>
         <v>Grupo 7</v>
       </c>
-      <c r="Q2" s="106"/>
+      <c r="Q2" s="103"/>
       <c r="R2" s="105" t="str">
         <f>Calificacion!J$4</f>
         <v>Grupo 8</v>
       </c>
-      <c r="S2" s="106"/>
+      <c r="S2" s="103"/>
       <c r="T2" s="105" t="str">
         <f>Calificacion!K$4</f>
         <v>Grupo 9</v>
       </c>
-      <c r="U2" s="106"/>
+      <c r="U2" s="103"/>
       <c r="V2" s="105" t="str">
         <f>Calificacion!L$4</f>
         <v>Grupo 10</v>
       </c>
-      <c r="W2" s="106"/>
+      <c r="W2" s="103"/>
       <c r="X2" s="105" t="str">
         <f>Calificacion!M$4</f>
         <v>Grupo 11</v>
       </c>
-      <c r="Y2" s="106"/>
+      <c r="Y2" s="103"/>
       <c r="Z2" s="105" t="str">
         <f>Calificacion!N$4</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AA2" s="106"/>
-      <c r="AB2" s="108" t="str">
+      <c r="AA2" s="103"/>
+      <c r="AB2" s="102" t="str">
         <f>Calificacion!O$4</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AC2" s="106"/>
-      <c r="AD2" s="108" t="str">
+      <c r="AC2" s="103"/>
+      <c r="AD2" s="102" t="str">
         <f>Calificacion!P$4</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AE2" s="106"/>
+      <c r="AE2" s="103"/>
     </row>
     <row r="3" spans="1:48" x14ac:dyDescent="0.45">
       <c r="B3" s="21" t="s">
@@ -5901,101 +5908,115 @@
       <c r="AE8" s="73"/>
     </row>
     <row r="9" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B9" s="107" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="107"/>
-      <c r="D9" s="103">
+      <c r="B9" s="106" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="106"/>
+      <c r="D9" s="104">
         <f>AVERAGE(D4:D8)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="103"/>
-      <c r="F9" s="103">
+      <c r="E9" s="104"/>
+      <c r="F9" s="104">
         <f>AVERAGE(F4:F8)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="103"/>
-      <c r="H9" s="103">
+      <c r="G9" s="104"/>
+      <c r="H9" s="104">
         <f>AVERAGE(H4:H8)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="103"/>
-      <c r="J9" s="103">
+      <c r="I9" s="104"/>
+      <c r="J9" s="104">
         <f>AVERAGE(J4:J8)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="103"/>
-      <c r="L9" s="103">
+      <c r="K9" s="104"/>
+      <c r="L9" s="104">
         <f>AVERAGE(L4:L8)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="103"/>
-      <c r="N9" s="103">
+      <c r="M9" s="104"/>
+      <c r="N9" s="104">
         <f>AVERAGE(N4:N8)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="103"/>
-      <c r="P9" s="103">
+      <c r="O9" s="104"/>
+      <c r="P9" s="104">
         <f>AVERAGE(P4:P8)</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="103"/>
-      <c r="R9" s="103">
+      <c r="Q9" s="104"/>
+      <c r="R9" s="104">
         <f>AVERAGE(R4:R8)</f>
         <v>0</v>
       </c>
-      <c r="S9" s="103"/>
-      <c r="T9" s="103">
+      <c r="S9" s="104"/>
+      <c r="T9" s="104">
         <f>AVERAGE(T4:T8)</f>
         <v>0</v>
       </c>
-      <c r="U9" s="103"/>
-      <c r="V9" s="103">
+      <c r="U9" s="104"/>
+      <c r="V9" s="104">
         <f>AVERAGE(V4:V8)</f>
         <v>0</v>
       </c>
-      <c r="W9" s="103"/>
-      <c r="X9" s="103">
+      <c r="W9" s="104"/>
+      <c r="X9" s="104">
         <f>AVERAGE(X4:X8)</f>
         <v>0</v>
       </c>
-      <c r="Y9" s="103"/>
-      <c r="Z9" s="103">
+      <c r="Y9" s="104"/>
+      <c r="Z9" s="104">
         <f>AVERAGE(Z4:Z8)</f>
         <v>0</v>
       </c>
-      <c r="AA9" s="103"/>
-      <c r="AB9" s="103">
+      <c r="AA9" s="104"/>
+      <c r="AB9" s="104">
         <f>AVERAGE(AB4:AB8)</f>
         <v>0</v>
       </c>
-      <c r="AC9" s="103"/>
-      <c r="AD9" s="103">
+      <c r="AC9" s="104"/>
+      <c r="AD9" s="104">
         <f>AVERAGE(AD4:AD8)</f>
         <v>0</v>
       </c>
-      <c r="AE9" s="103"/>
+      <c r="AE9" s="104"/>
     </row>
     <row r="10" spans="1:48" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="104" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" s="104"/>
+      <c r="B10" s="107" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="107"/>
     </row>
     <row r="11" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B11" s="104"/>
-      <c r="C11" s="104"/>
+      <c r="B11" s="107"/>
+      <c r="C11" s="107"/>
     </row>
     <row r="12" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B12" s="104"/>
-      <c r="C12" s="104"/>
+      <c r="B12" s="107"/>
+      <c r="C12" s="107"/>
     </row>
     <row r="13" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B13" s="104"/>
-      <c r="C13" s="104"/>
+      <c r="B13" s="107"/>
+      <c r="C13" s="107"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="B10:C13"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:K9"/>
     <mergeCell ref="AD2:AE2"/>
     <mergeCell ref="AD9:AE9"/>
     <mergeCell ref="L2:M2"/>
@@ -6012,20 +6033,6 @@
     <mergeCell ref="Z9:AA9"/>
     <mergeCell ref="AB9:AC9"/>
     <mergeCell ref="L9:M9"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="B10:C13"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6142,71 +6149,71 @@
         <f>Calificacion!C$4</f>
         <v>Grupo 1</v>
       </c>
-      <c r="E2" s="106"/>
+      <c r="E2" s="103"/>
       <c r="F2" s="105" t="str">
         <f>Calificacion!D$4</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="106"/>
+      <c r="G2" s="103"/>
       <c r="H2" s="105" t="str">
         <f>Calificacion!E$4</f>
         <v>Grupo 3</v>
       </c>
-      <c r="I2" s="106"/>
+      <c r="I2" s="103"/>
       <c r="J2" s="105" t="str">
         <f>Calificacion!F$4</f>
         <v>Grupo 4</v>
       </c>
-      <c r="K2" s="106"/>
+      <c r="K2" s="103"/>
       <c r="L2" s="105" t="str">
         <f>Calificacion!G$4</f>
         <v>Grupo 5</v>
       </c>
-      <c r="M2" s="106"/>
+      <c r="M2" s="103"/>
       <c r="N2" s="105" t="str">
         <f>Calificacion!H$4</f>
         <v>Grupo 6</v>
       </c>
-      <c r="O2" s="106"/>
+      <c r="O2" s="103"/>
       <c r="P2" s="105" t="str">
         <f>Calificacion!I$4</f>
         <v>Grupo 7</v>
       </c>
-      <c r="Q2" s="106"/>
+      <c r="Q2" s="103"/>
       <c r="R2" s="105" t="str">
         <f>Calificacion!J$4</f>
         <v>Grupo 8</v>
       </c>
-      <c r="S2" s="106"/>
+      <c r="S2" s="103"/>
       <c r="T2" s="105" t="str">
         <f>Calificacion!K$4</f>
         <v>Grupo 9</v>
       </c>
-      <c r="U2" s="106"/>
+      <c r="U2" s="103"/>
       <c r="V2" s="105" t="str">
         <f>Calificacion!L$4</f>
         <v>Grupo 10</v>
       </c>
-      <c r="W2" s="106"/>
+      <c r="W2" s="103"/>
       <c r="X2" s="105" t="str">
         <f>Calificacion!M$4</f>
         <v>Grupo 11</v>
       </c>
-      <c r="Y2" s="106"/>
-      <c r="Z2" s="108" t="str">
+      <c r="Y2" s="103"/>
+      <c r="Z2" s="102" t="str">
         <f>Calificacion!N$4</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AA2" s="106"/>
-      <c r="AB2" s="108" t="str">
+      <c r="AA2" s="103"/>
+      <c r="AB2" s="102" t="str">
         <f>Calificacion!O$4</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AC2" s="106"/>
+      <c r="AC2" s="103"/>
       <c r="AD2" s="105" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE2" s="106"/>
+        <v>83</v>
+      </c>
+      <c r="AE2" s="103"/>
     </row>
     <row r="3" spans="1:48" x14ac:dyDescent="0.45">
       <c r="B3" s="21" t="s">
@@ -6613,115 +6620,115 @@
       <c r="AE11" s="73"/>
     </row>
     <row r="12" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B12" s="107" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" s="107"/>
-      <c r="D12" s="103">
+      <c r="B12" s="106" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="106"/>
+      <c r="D12" s="104">
         <f>AVERAGE(D4:D11)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="103"/>
-      <c r="F12" s="103">
+      <c r="E12" s="104"/>
+      <c r="F12" s="104">
         <f>AVERAGE(F4:F11)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="103"/>
-      <c r="H12" s="103">
+      <c r="G12" s="104"/>
+      <c r="H12" s="104">
         <f>AVERAGE(H4:H11)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="103"/>
-      <c r="J12" s="103">
+      <c r="I12" s="104"/>
+      <c r="J12" s="104">
         <f>AVERAGE(J4:J11)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="103"/>
-      <c r="L12" s="103">
+      <c r="K12" s="104"/>
+      <c r="L12" s="104">
         <f>AVERAGE(L4:L11)</f>
         <v>0</v>
       </c>
-      <c r="M12" s="103"/>
-      <c r="N12" s="103">
+      <c r="M12" s="104"/>
+      <c r="N12" s="104">
         <f>AVERAGE(N4:N11)</f>
         <v>0</v>
       </c>
-      <c r="O12" s="103"/>
-      <c r="P12" s="103">
+      <c r="O12" s="104"/>
+      <c r="P12" s="104">
         <f>AVERAGE(P4:P11)</f>
         <v>0</v>
       </c>
-      <c r="Q12" s="103"/>
-      <c r="R12" s="103">
+      <c r="Q12" s="104"/>
+      <c r="R12" s="104">
         <f>AVERAGE(R4:R11)</f>
         <v>0</v>
       </c>
-      <c r="S12" s="103"/>
-      <c r="T12" s="103">
+      <c r="S12" s="104"/>
+      <c r="T12" s="104">
         <f>AVERAGE(T4:T11)</f>
         <v>0</v>
       </c>
-      <c r="U12" s="103"/>
-      <c r="V12" s="103">
+      <c r="U12" s="104"/>
+      <c r="V12" s="104">
         <f>AVERAGE(V4:V11)</f>
         <v>0</v>
       </c>
-      <c r="W12" s="103"/>
-      <c r="X12" s="103">
+      <c r="W12" s="104"/>
+      <c r="X12" s="104">
         <f>AVERAGE(X4:X11)</f>
         <v>0</v>
       </c>
-      <c r="Y12" s="103"/>
-      <c r="Z12" s="103">
+      <c r="Y12" s="104"/>
+      <c r="Z12" s="104">
         <f>AVERAGE(Z4:Z11)</f>
         <v>0</v>
       </c>
-      <c r="AA12" s="103"/>
-      <c r="AB12" s="103">
+      <c r="AA12" s="104"/>
+      <c r="AB12" s="104">
         <f>AVERAGE(AB4:AB11)</f>
         <v>0</v>
       </c>
-      <c r="AC12" s="103"/>
-      <c r="AD12" s="103">
+      <c r="AC12" s="104"/>
+      <c r="AD12" s="104">
         <f>AVERAGE(AD4:AD11)</f>
         <v>0</v>
       </c>
-      <c r="AE12" s="103"/>
+      <c r="AE12" s="104"/>
     </row>
     <row r="13" spans="1:48" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B13" s="109" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="109"/>
+      <c r="B13" s="108" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="108"/>
     </row>
     <row r="14" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B14" s="104"/>
-      <c r="C14" s="104"/>
+      <c r="B14" s="107"/>
+      <c r="C14" s="107"/>
     </row>
     <row r="15" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B15" s="104"/>
-      <c r="C15" s="104"/>
+      <c r="B15" s="107"/>
+      <c r="C15" s="107"/>
     </row>
     <row r="16" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B16" s="104"/>
-      <c r="C16" s="104"/>
+      <c r="B16" s="107"/>
+      <c r="C16" s="107"/>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B17" s="104"/>
-      <c r="C17" s="104"/>
+      <c r="B17" s="107"/>
+      <c r="C17" s="107"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="AB12:AC12"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="Z12:AA12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="B13:C17"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="X2:Y2"/>
     <mergeCell ref="AB2:AC2"/>
@@ -6732,16 +6739,16 @@
     <mergeCell ref="T2:U2"/>
     <mergeCell ref="V2:W2"/>
     <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="B13:C17"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="AB12:AC12"/>
+    <mergeCell ref="AD12:AE12"/>
+    <mergeCell ref="Z12:AA12"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6858,72 +6865,72 @@
         <f>Calificacion!C$4</f>
         <v>Grupo 1</v>
       </c>
-      <c r="E2" s="106"/>
+      <c r="E2" s="103"/>
       <c r="F2" s="105" t="str">
         <f>Calificacion!D$4</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="106"/>
+      <c r="G2" s="103"/>
       <c r="H2" s="105" t="str">
         <f>Calificacion!E$4</f>
         <v>Grupo 3</v>
       </c>
-      <c r="I2" s="106"/>
+      <c r="I2" s="103"/>
       <c r="J2" s="105" t="str">
         <f>Calificacion!F$4</f>
         <v>Grupo 4</v>
       </c>
-      <c r="K2" s="106"/>
+      <c r="K2" s="103"/>
       <c r="L2" s="105" t="str">
         <f>Calificacion!G$4</f>
         <v>Grupo 5</v>
       </c>
-      <c r="M2" s="106"/>
+      <c r="M2" s="103"/>
       <c r="N2" s="105" t="str">
         <f>Calificacion!H$4</f>
         <v>Grupo 6</v>
       </c>
-      <c r="O2" s="106"/>
+      <c r="O2" s="103"/>
       <c r="P2" s="105" t="str">
         <f>Calificacion!I$4</f>
         <v>Grupo 7</v>
       </c>
-      <c r="Q2" s="106"/>
+      <c r="Q2" s="103"/>
       <c r="R2" s="105" t="str">
         <f>Calificacion!J$4</f>
         <v>Grupo 8</v>
       </c>
-      <c r="S2" s="106"/>
+      <c r="S2" s="103"/>
       <c r="T2" s="105" t="str">
         <f>Calificacion!K$4</f>
         <v>Grupo 9</v>
       </c>
-      <c r="U2" s="106"/>
+      <c r="U2" s="103"/>
       <c r="V2" s="105" t="str">
         <f>Calificacion!L$4</f>
         <v>Grupo 10</v>
       </c>
-      <c r="W2" s="106"/>
+      <c r="W2" s="103"/>
       <c r="X2" s="105" t="str">
         <f>Calificacion!M$4</f>
         <v>Grupo 11</v>
       </c>
-      <c r="Y2" s="106"/>
+      <c r="Y2" s="103"/>
       <c r="Z2" s="105" t="str">
         <f>Calificacion!N$4</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AA2" s="106"/>
-      <c r="AB2" s="108" t="str">
+      <c r="AA2" s="103"/>
+      <c r="AB2" s="102" t="str">
         <f>Calificacion!O$4</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AC2" s="106"/>
+      <c r="AC2" s="103"/>
       <c r="AD2" s="105" t="str">
         <f>Calificacion!P$4</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AE2" s="106"/>
+      <c r="AE2" s="103"/>
     </row>
     <row r="3" spans="1:48" x14ac:dyDescent="0.45">
       <c r="B3" s="21" t="s">
@@ -7330,115 +7337,115 @@
       <c r="AE11" s="73"/>
     </row>
     <row r="12" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B12" s="107" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" s="107"/>
-      <c r="D12" s="103">
+      <c r="B12" s="106" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="106"/>
+      <c r="D12" s="104">
         <f>AVERAGE(D4:D11)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="103"/>
-      <c r="F12" s="103">
+      <c r="E12" s="104"/>
+      <c r="F12" s="104">
         <f>AVERAGE(F4:F11)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="103"/>
-      <c r="H12" s="103">
+      <c r="G12" s="104"/>
+      <c r="H12" s="104">
         <f>AVERAGE(H4:H11)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="103"/>
-      <c r="J12" s="103">
+      <c r="I12" s="104"/>
+      <c r="J12" s="104">
         <f>AVERAGE(J4:J11)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="103"/>
-      <c r="L12" s="103">
+      <c r="K12" s="104"/>
+      <c r="L12" s="104">
         <f>AVERAGE(L4:L11)</f>
         <v>0</v>
       </c>
-      <c r="M12" s="103"/>
-      <c r="N12" s="103">
+      <c r="M12" s="104"/>
+      <c r="N12" s="104">
         <f>AVERAGE(N4:N11)</f>
         <v>0</v>
       </c>
-      <c r="O12" s="103"/>
-      <c r="P12" s="103">
+      <c r="O12" s="104"/>
+      <c r="P12" s="104">
         <f>AVERAGE(P4:P11)</f>
         <v>0</v>
       </c>
-      <c r="Q12" s="103"/>
-      <c r="R12" s="103">
+      <c r="Q12" s="104"/>
+      <c r="R12" s="104">
         <f>AVERAGE(R4:R11)</f>
         <v>0</v>
       </c>
-      <c r="S12" s="103"/>
-      <c r="T12" s="103">
+      <c r="S12" s="104"/>
+      <c r="T12" s="104">
         <f>AVERAGE(T4:T11)</f>
         <v>0</v>
       </c>
-      <c r="U12" s="103"/>
-      <c r="V12" s="103">
+      <c r="U12" s="104"/>
+      <c r="V12" s="104">
         <f>AVERAGE(V4:V11)</f>
         <v>0</v>
       </c>
-      <c r="W12" s="103"/>
-      <c r="X12" s="103">
+      <c r="W12" s="104"/>
+      <c r="X12" s="104">
         <f>AVERAGE(X4:X11)</f>
         <v>0</v>
       </c>
-      <c r="Y12" s="103"/>
-      <c r="Z12" s="103">
+      <c r="Y12" s="104"/>
+      <c r="Z12" s="104">
         <f>AVERAGE(Z4:Z11)</f>
         <v>0</v>
       </c>
-      <c r="AA12" s="103"/>
-      <c r="AB12" s="103">
+      <c r="AA12" s="104"/>
+      <c r="AB12" s="104">
         <f>AVERAGE(AB4:AB11)</f>
         <v>0</v>
       </c>
-      <c r="AC12" s="103"/>
-      <c r="AD12" s="103">
+      <c r="AC12" s="104"/>
+      <c r="AD12" s="104">
         <f>AVERAGE(AD4:AD11)</f>
         <v>0</v>
       </c>
-      <c r="AE12" s="103"/>
+      <c r="AE12" s="104"/>
     </row>
     <row r="13" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B13" s="109" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="109"/>
+      <c r="B13" s="108" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="108"/>
     </row>
     <row r="14" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B14" s="104"/>
-      <c r="C14" s="104"/>
+      <c r="B14" s="107"/>
+      <c r="C14" s="107"/>
     </row>
     <row r="15" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B15" s="104"/>
-      <c r="C15" s="104"/>
+      <c r="B15" s="107"/>
+      <c r="C15" s="107"/>
     </row>
     <row r="16" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B16" s="104"/>
-      <c r="C16" s="104"/>
+      <c r="B16" s="107"/>
+      <c r="C16" s="107"/>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B17" s="104"/>
-      <c r="C17" s="104"/>
+      <c r="B17" s="107"/>
+      <c r="C17" s="107"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="Z12:AA12"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="AB12:AC12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="B13:C17"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="X2:Y2"/>
     <mergeCell ref="Z2:AA2"/>
@@ -7449,16 +7456,16 @@
     <mergeCell ref="T2:U2"/>
     <mergeCell ref="V2:W2"/>
     <mergeCell ref="AB2:AC2"/>
-    <mergeCell ref="B13:C17"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="Z12:AA12"/>
+    <mergeCell ref="AD12:AE12"/>
+    <mergeCell ref="AB12:AC12"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/activity/M01A01/M01A01_Parametros.xlsx
+++ b/activity/M01A01/M01A01_Parametros.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA022F2A-5C7F-4563-89D2-6FF263312DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED3BB8C-D6FA-45A8-93E2-38DB4C3FD9D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="773" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="773" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="11" r:id="rId1"/>
@@ -1180,9 +1180,36 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1192,56 +1219,29 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="22" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="22" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3044,23 +3044,23 @@
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="B2" s="91" t="s">
+      <c r="B2" s="93" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="91"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
-      <c r="H2" s="91"/>
-      <c r="I2" s="91"/>
-      <c r="J2" s="91"/>
-      <c r="K2" s="91"/>
-      <c r="L2" s="91"/>
-      <c r="M2" s="91"/>
-      <c r="N2" s="91"/>
-      <c r="O2" s="91"/>
-      <c r="P2" s="91"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="93"/>
+      <c r="K2" s="93"/>
+      <c r="L2" s="93"/>
+      <c r="M2" s="93"/>
+      <c r="N2" s="93"/>
+      <c r="O2" s="93"/>
+      <c r="P2" s="93"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.45">
       <c r="B3" s="65" t="s">
@@ -3543,41 +3543,41 @@
       </c>
     </row>
     <row r="12" spans="1:19" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="109" t="str">
+      <c r="B12" s="94" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",P1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",P1," en GitHub."))</f>
         <v>Ir a actividad M01A01 en GitHub.</v>
       </c>
-      <c r="C12" s="109"/>
-      <c r="D12" s="109"/>
-      <c r="E12" s="109"/>
-      <c r="F12" s="109"/>
-      <c r="G12" s="110"/>
-      <c r="H12" s="110"/>
-      <c r="I12" s="110"/>
-      <c r="J12" s="110"/>
-      <c r="K12" s="110"/>
-      <c r="L12" s="110"/>
-      <c r="M12" s="110"/>
-      <c r="N12" s="110"/>
-      <c r="O12" s="110"/>
-      <c r="P12" s="110"/>
+      <c r="C12" s="94"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="91"/>
+      <c r="H12" s="91"/>
+      <c r="I12" s="91"/>
+      <c r="J12" s="91"/>
+      <c r="K12" s="91"/>
+      <c r="L12" s="91"/>
+      <c r="M12" s="91"/>
+      <c r="N12" s="91"/>
+      <c r="O12" s="91"/>
+      <c r="P12" s="91"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="B13" s="109"/>
-      <c r="C13" s="109"/>
-      <c r="D13" s="109"/>
-      <c r="E13" s="109"/>
-      <c r="F13" s="109"/>
-      <c r="G13" s="111"/>
-      <c r="H13" s="111"/>
-      <c r="I13" s="111"/>
-      <c r="J13" s="111"/>
-      <c r="K13" s="111"/>
-      <c r="L13" s="111"/>
-      <c r="M13" s="111"/>
-      <c r="N13" s="111"/>
-      <c r="O13" s="111"/>
-      <c r="P13" s="111"/>
+      <c r="B13" s="94"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="94"/>
+      <c r="E13" s="94"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="92"/>
+      <c r="H13" s="92"/>
+      <c r="I13" s="92"/>
+      <c r="J13" s="92"/>
+      <c r="K13" s="92"/>
+      <c r="L13" s="92"/>
+      <c r="M13" s="92"/>
+      <c r="N13" s="92"/>
+      <c r="O13" s="92"/>
+      <c r="P13" s="92"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B18" s="13"/>
@@ -3728,90 +3728,90 @@
       <c r="E2" s="10"/>
       <c r="F2" s="10"/>
       <c r="G2" s="47"/>
-      <c r="H2" s="92" t="str">
+      <c r="H2" s="101" t="str">
         <f>Calificacion!C$4</f>
         <v>Grupo 1</v>
       </c>
-      <c r="I2" s="93"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="92" t="str">
+      <c r="I2" s="102"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="101" t="str">
         <f>Calificacion!D$4</f>
         <v>Grupo 2</v>
       </c>
-      <c r="L2" s="93"/>
-      <c r="M2" s="94"/>
-      <c r="N2" s="92" t="str">
+      <c r="L2" s="102"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="101" t="str">
         <f>Calificacion!E$4</f>
         <v>Grupo 3</v>
       </c>
-      <c r="O2" s="93"/>
-      <c r="P2" s="94"/>
-      <c r="Q2" s="92" t="str">
+      <c r="O2" s="102"/>
+      <c r="P2" s="103"/>
+      <c r="Q2" s="101" t="str">
         <f>Calificacion!F$4</f>
         <v>Grupo 4</v>
       </c>
-      <c r="R2" s="93"/>
-      <c r="S2" s="94"/>
-      <c r="T2" s="92" t="str">
+      <c r="R2" s="102"/>
+      <c r="S2" s="103"/>
+      <c r="T2" s="101" t="str">
         <f>Calificacion!G$4</f>
         <v>Grupo 5</v>
       </c>
-      <c r="U2" s="93"/>
-      <c r="V2" s="94"/>
-      <c r="W2" s="92" t="str">
+      <c r="U2" s="102"/>
+      <c r="V2" s="103"/>
+      <c r="W2" s="101" t="str">
         <f>Calificacion!H$4</f>
         <v>Grupo 6</v>
       </c>
-      <c r="X2" s="93"/>
-      <c r="Y2" s="94"/>
-      <c r="Z2" s="92" t="str">
+      <c r="X2" s="102"/>
+      <c r="Y2" s="103"/>
+      <c r="Z2" s="101" t="str">
         <f>Calificacion!I$4</f>
         <v>Grupo 7</v>
       </c>
-      <c r="AA2" s="93"/>
-      <c r="AB2" s="94"/>
-      <c r="AC2" s="92" t="str">
+      <c r="AA2" s="102"/>
+      <c r="AB2" s="103"/>
+      <c r="AC2" s="101" t="str">
         <f>Calificacion!J$4</f>
         <v>Grupo 8</v>
       </c>
-      <c r="AD2" s="93"/>
-      <c r="AE2" s="94"/>
-      <c r="AF2" s="92" t="str">
+      <c r="AD2" s="102"/>
+      <c r="AE2" s="103"/>
+      <c r="AF2" s="101" t="str">
         <f>Calificacion!K$4</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AG2" s="93"/>
-      <c r="AH2" s="94"/>
-      <c r="AI2" s="92" t="str">
+      <c r="AG2" s="102"/>
+      <c r="AH2" s="103"/>
+      <c r="AI2" s="101" t="str">
         <f>Calificacion!L$4</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AJ2" s="93"/>
-      <c r="AK2" s="94"/>
-      <c r="AL2" s="92" t="str">
+      <c r="AJ2" s="102"/>
+      <c r="AK2" s="103"/>
+      <c r="AL2" s="101" t="str">
         <f>Calificacion!M$4</f>
         <v>Grupo 11</v>
       </c>
-      <c r="AM2" s="93"/>
-      <c r="AN2" s="94"/>
-      <c r="AO2" s="92" t="str">
+      <c r="AM2" s="102"/>
+      <c r="AN2" s="103"/>
+      <c r="AO2" s="101" t="str">
         <f>Calificacion!N$4</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AP2" s="93"/>
-      <c r="AQ2" s="94"/>
-      <c r="AR2" s="92" t="str">
+      <c r="AP2" s="102"/>
+      <c r="AQ2" s="103"/>
+      <c r="AR2" s="101" t="str">
         <f>Calificacion!O$4</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AS2" s="93"/>
-      <c r="AT2" s="94"/>
-      <c r="AU2" s="92" t="str">
+      <c r="AS2" s="102"/>
+      <c r="AT2" s="103"/>
+      <c r="AU2" s="101" t="str">
         <f>Calificacion!P$4</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AV2" s="93"/>
-      <c r="AW2" s="94"/>
+      <c r="AV2" s="102"/>
+      <c r="AW2" s="103"/>
     </row>
     <row r="3" spans="1:49" x14ac:dyDescent="0.45">
       <c r="B3" s="33" t="s">
@@ -4930,14 +4930,14 @@
       <c r="AW19" s="82"/>
     </row>
     <row r="20" spans="2:49" ht="17.2" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="101" t="s">
+      <c r="B20" s="110" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="101"/>
-      <c r="D20" s="101"/>
-      <c r="E20" s="101"/>
-      <c r="F20" s="101"/>
-      <c r="G20" s="101"/>
+      <c r="C20" s="110"/>
+      <c r="D20" s="110"/>
+      <c r="E20" s="110"/>
+      <c r="F20" s="110"/>
+      <c r="G20" s="110"/>
       <c r="H20" s="95">
         <f>AVERAGE(H4:H19)</f>
         <v>0</v>
@@ -5397,23 +5397,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="Q20:S20"/>
-    <mergeCell ref="T20:V20"/>
-    <mergeCell ref="W20:Y20"/>
-    <mergeCell ref="Z20:AB20"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="B9:B19"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="T2:V2"/>
-    <mergeCell ref="W2:Y2"/>
-    <mergeCell ref="Z2:AB2"/>
     <mergeCell ref="AU2:AW2"/>
     <mergeCell ref="AR2:AT2"/>
     <mergeCell ref="AR20:AT20"/>
@@ -5428,6 +5411,23 @@
     <mergeCell ref="AI20:AK20"/>
     <mergeCell ref="AL20:AN20"/>
     <mergeCell ref="AO20:AQ20"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="B9:B19"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="Q20:S20"/>
+    <mergeCell ref="T20:V20"/>
+    <mergeCell ref="W20:Y20"/>
+    <mergeCell ref="Z20:AB20"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5540,76 +5540,76 @@
         <v>62</v>
       </c>
       <c r="C2" s="51"/>
-      <c r="D2" s="105" t="str">
+      <c r="D2" s="106" t="str">
         <f>Calificacion!C$4</f>
         <v>Grupo 1</v>
       </c>
-      <c r="E2" s="103"/>
-      <c r="F2" s="105" t="str">
+      <c r="E2" s="107"/>
+      <c r="F2" s="106" t="str">
         <f>Calificacion!D$4</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="105" t="str">
+      <c r="G2" s="107"/>
+      <c r="H2" s="106" t="str">
         <f>Calificacion!E$4</f>
         <v>Grupo 3</v>
       </c>
-      <c r="I2" s="103"/>
-      <c r="J2" s="105" t="str">
+      <c r="I2" s="107"/>
+      <c r="J2" s="106" t="str">
         <f>Calificacion!F$4</f>
         <v>Grupo 4</v>
       </c>
-      <c r="K2" s="103"/>
-      <c r="L2" s="105" t="str">
+      <c r="K2" s="107"/>
+      <c r="L2" s="106" t="str">
         <f>Calificacion!G$4</f>
         <v>Grupo 5</v>
       </c>
-      <c r="M2" s="103"/>
-      <c r="N2" s="105" t="str">
+      <c r="M2" s="107"/>
+      <c r="N2" s="106" t="str">
         <f>Calificacion!H$4</f>
         <v>Grupo 6</v>
       </c>
-      <c r="O2" s="103"/>
-      <c r="P2" s="105" t="str">
+      <c r="O2" s="107"/>
+      <c r="P2" s="106" t="str">
         <f>Calificacion!I$4</f>
         <v>Grupo 7</v>
       </c>
-      <c r="Q2" s="103"/>
-      <c r="R2" s="105" t="str">
+      <c r="Q2" s="107"/>
+      <c r="R2" s="106" t="str">
         <f>Calificacion!J$4</f>
         <v>Grupo 8</v>
       </c>
-      <c r="S2" s="103"/>
-      <c r="T2" s="105" t="str">
+      <c r="S2" s="107"/>
+      <c r="T2" s="106" t="str">
         <f>Calificacion!K$4</f>
         <v>Grupo 9</v>
       </c>
-      <c r="U2" s="103"/>
-      <c r="V2" s="105" t="str">
+      <c r="U2" s="107"/>
+      <c r="V2" s="106" t="str">
         <f>Calificacion!L$4</f>
         <v>Grupo 10</v>
       </c>
-      <c r="W2" s="103"/>
-      <c r="X2" s="105" t="str">
+      <c r="W2" s="107"/>
+      <c r="X2" s="106" t="str">
         <f>Calificacion!M$4</f>
         <v>Grupo 11</v>
       </c>
-      <c r="Y2" s="103"/>
-      <c r="Z2" s="105" t="str">
+      <c r="Y2" s="107"/>
+      <c r="Z2" s="106" t="str">
         <f>Calificacion!N$4</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AA2" s="103"/>
-      <c r="AB2" s="102" t="str">
+      <c r="AA2" s="107"/>
+      <c r="AB2" s="108" t="str">
         <f>Calificacion!O$4</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AC2" s="103"/>
-      <c r="AD2" s="102" t="str">
+      <c r="AC2" s="107"/>
+      <c r="AD2" s="108" t="str">
         <f>Calificacion!P$4</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AE2" s="103"/>
+      <c r="AE2" s="107"/>
     </row>
     <row r="3" spans="1:48" x14ac:dyDescent="0.45">
       <c r="B3" s="21" t="s">
@@ -5908,10 +5908,10 @@
       <c r="AE8" s="73"/>
     </row>
     <row r="9" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B9" s="106" t="s">
+      <c r="B9" s="111" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="106"/>
+      <c r="C9" s="111"/>
       <c r="D9" s="104">
         <f>AVERAGE(D4:D8)</f>
         <v>0</v>
@@ -5984,39 +5984,25 @@
       <c r="AE9" s="104"/>
     </row>
     <row r="10" spans="1:48" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="107" t="s">
+      <c r="B10" s="105" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="107"/>
+      <c r="C10" s="105"/>
     </row>
     <row r="11" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B11" s="107"/>
-      <c r="C11" s="107"/>
+      <c r="B11" s="105"/>
+      <c r="C11" s="105"/>
     </row>
     <row r="12" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B12" s="107"/>
-      <c r="C12" s="107"/>
+      <c r="B12" s="105"/>
+      <c r="C12" s="105"/>
     </row>
     <row r="13" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B13" s="107"/>
-      <c r="C13" s="107"/>
+      <c r="B13" s="105"/>
+      <c r="C13" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="B10:C13"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="J9:K9"/>
     <mergeCell ref="AD2:AE2"/>
     <mergeCell ref="AD9:AE9"/>
     <mergeCell ref="L2:M2"/>
@@ -6033,6 +6019,20 @@
     <mergeCell ref="Z9:AA9"/>
     <mergeCell ref="AB9:AC9"/>
     <mergeCell ref="L9:M9"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="B10:C13"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6145,75 +6145,75 @@
         <v>61</v>
       </c>
       <c r="C2" s="51"/>
-      <c r="D2" s="105" t="str">
+      <c r="D2" s="106" t="str">
         <f>Calificacion!C$4</f>
         <v>Grupo 1</v>
       </c>
-      <c r="E2" s="103"/>
-      <c r="F2" s="105" t="str">
+      <c r="E2" s="107"/>
+      <c r="F2" s="106" t="str">
         <f>Calificacion!D$4</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="105" t="str">
+      <c r="G2" s="107"/>
+      <c r="H2" s="106" t="str">
         <f>Calificacion!E$4</f>
         <v>Grupo 3</v>
       </c>
-      <c r="I2" s="103"/>
-      <c r="J2" s="105" t="str">
+      <c r="I2" s="107"/>
+      <c r="J2" s="106" t="str">
         <f>Calificacion!F$4</f>
         <v>Grupo 4</v>
       </c>
-      <c r="K2" s="103"/>
-      <c r="L2" s="105" t="str">
+      <c r="K2" s="107"/>
+      <c r="L2" s="106" t="str">
         <f>Calificacion!G$4</f>
         <v>Grupo 5</v>
       </c>
-      <c r="M2" s="103"/>
-      <c r="N2" s="105" t="str">
+      <c r="M2" s="107"/>
+      <c r="N2" s="106" t="str">
         <f>Calificacion!H$4</f>
         <v>Grupo 6</v>
       </c>
-      <c r="O2" s="103"/>
-      <c r="P2" s="105" t="str">
+      <c r="O2" s="107"/>
+      <c r="P2" s="106" t="str">
         <f>Calificacion!I$4</f>
         <v>Grupo 7</v>
       </c>
-      <c r="Q2" s="103"/>
-      <c r="R2" s="105" t="str">
+      <c r="Q2" s="107"/>
+      <c r="R2" s="106" t="str">
         <f>Calificacion!J$4</f>
         <v>Grupo 8</v>
       </c>
-      <c r="S2" s="103"/>
-      <c r="T2" s="105" t="str">
+      <c r="S2" s="107"/>
+      <c r="T2" s="106" t="str">
         <f>Calificacion!K$4</f>
         <v>Grupo 9</v>
       </c>
-      <c r="U2" s="103"/>
-      <c r="V2" s="105" t="str">
+      <c r="U2" s="107"/>
+      <c r="V2" s="106" t="str">
         <f>Calificacion!L$4</f>
         <v>Grupo 10</v>
       </c>
-      <c r="W2" s="103"/>
-      <c r="X2" s="105" t="str">
+      <c r="W2" s="107"/>
+      <c r="X2" s="106" t="str">
         <f>Calificacion!M$4</f>
         <v>Grupo 11</v>
       </c>
-      <c r="Y2" s="103"/>
-      <c r="Z2" s="102" t="str">
+      <c r="Y2" s="107"/>
+      <c r="Z2" s="108" t="str">
         <f>Calificacion!N$4</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AA2" s="103"/>
-      <c r="AB2" s="102" t="str">
+      <c r="AA2" s="107"/>
+      <c r="AB2" s="108" t="str">
         <f>Calificacion!O$4</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AC2" s="103"/>
-      <c r="AD2" s="105" t="s">
+      <c r="AC2" s="107"/>
+      <c r="AD2" s="106" t="s">
         <v>83</v>
       </c>
-      <c r="AE2" s="103"/>
+      <c r="AE2" s="107"/>
     </row>
     <row r="3" spans="1:48" x14ac:dyDescent="0.45">
       <c r="B3" s="21" t="s">
@@ -6620,10 +6620,10 @@
       <c r="AE11" s="73"/>
     </row>
     <row r="12" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B12" s="106" t="s">
+      <c r="B12" s="111" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="106"/>
+      <c r="C12" s="111"/>
       <c r="D12" s="104">
         <f>AVERAGE(D4:D11)</f>
         <v>0</v>
@@ -6696,29 +6696,49 @@
       <c r="AE12" s="104"/>
     </row>
     <row r="13" spans="1:48" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B13" s="108" t="s">
+      <c r="B13" s="109" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="108"/>
+      <c r="C13" s="109"/>
     </row>
     <row r="14" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B14" s="107"/>
-      <c r="C14" s="107"/>
+      <c r="B14" s="105"/>
+      <c r="C14" s="105"/>
     </row>
     <row r="15" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B15" s="107"/>
-      <c r="C15" s="107"/>
+      <c r="B15" s="105"/>
+      <c r="C15" s="105"/>
     </row>
     <row r="16" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B16" s="107"/>
-      <c r="C16" s="107"/>
+      <c r="B16" s="105"/>
+      <c r="C16" s="105"/>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B17" s="107"/>
-      <c r="C17" s="107"/>
+      <c r="B17" s="105"/>
+      <c r="C17" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="AB12:AC12"/>
+    <mergeCell ref="AD12:AE12"/>
+    <mergeCell ref="Z12:AA12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="AB2:AC2"/>
+    <mergeCell ref="AD2:AE2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="Z2:AA2"/>
     <mergeCell ref="B13:C17"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:G2"/>
@@ -6729,26 +6749,6 @@
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="H12:I12"/>
     <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="AB2:AC2"/>
-    <mergeCell ref="AD2:AE2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="V2:W2"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="AB12:AC12"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="Z12:AA12"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6861,76 +6861,76 @@
         <v>60</v>
       </c>
       <c r="C2" s="51"/>
-      <c r="D2" s="105" t="str">
+      <c r="D2" s="106" t="str">
         <f>Calificacion!C$4</f>
         <v>Grupo 1</v>
       </c>
-      <c r="E2" s="103"/>
-      <c r="F2" s="105" t="str">
+      <c r="E2" s="107"/>
+      <c r="F2" s="106" t="str">
         <f>Calificacion!D$4</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="105" t="str">
+      <c r="G2" s="107"/>
+      <c r="H2" s="106" t="str">
         <f>Calificacion!E$4</f>
         <v>Grupo 3</v>
       </c>
-      <c r="I2" s="103"/>
-      <c r="J2" s="105" t="str">
+      <c r="I2" s="107"/>
+      <c r="J2" s="106" t="str">
         <f>Calificacion!F$4</f>
         <v>Grupo 4</v>
       </c>
-      <c r="K2" s="103"/>
-      <c r="L2" s="105" t="str">
+      <c r="K2" s="107"/>
+      <c r="L2" s="106" t="str">
         <f>Calificacion!G$4</f>
         <v>Grupo 5</v>
       </c>
-      <c r="M2" s="103"/>
-      <c r="N2" s="105" t="str">
+      <c r="M2" s="107"/>
+      <c r="N2" s="106" t="str">
         <f>Calificacion!H$4</f>
         <v>Grupo 6</v>
       </c>
-      <c r="O2" s="103"/>
-      <c r="P2" s="105" t="str">
+      <c r="O2" s="107"/>
+      <c r="P2" s="106" t="str">
         <f>Calificacion!I$4</f>
         <v>Grupo 7</v>
       </c>
-      <c r="Q2" s="103"/>
-      <c r="R2" s="105" t="str">
+      <c r="Q2" s="107"/>
+      <c r="R2" s="106" t="str">
         <f>Calificacion!J$4</f>
         <v>Grupo 8</v>
       </c>
-      <c r="S2" s="103"/>
-      <c r="T2" s="105" t="str">
+      <c r="S2" s="107"/>
+      <c r="T2" s="106" t="str">
         <f>Calificacion!K$4</f>
         <v>Grupo 9</v>
       </c>
-      <c r="U2" s="103"/>
-      <c r="V2" s="105" t="str">
+      <c r="U2" s="107"/>
+      <c r="V2" s="106" t="str">
         <f>Calificacion!L$4</f>
         <v>Grupo 10</v>
       </c>
-      <c r="W2" s="103"/>
-      <c r="X2" s="105" t="str">
+      <c r="W2" s="107"/>
+      <c r="X2" s="106" t="str">
         <f>Calificacion!M$4</f>
         <v>Grupo 11</v>
       </c>
-      <c r="Y2" s="103"/>
-      <c r="Z2" s="105" t="str">
+      <c r="Y2" s="107"/>
+      <c r="Z2" s="106" t="str">
         <f>Calificacion!N$4</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AA2" s="103"/>
-      <c r="AB2" s="102" t="str">
+      <c r="AA2" s="107"/>
+      <c r="AB2" s="108" t="str">
         <f>Calificacion!O$4</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AC2" s="103"/>
-      <c r="AD2" s="105" t="str">
+      <c r="AC2" s="107"/>
+      <c r="AD2" s="106" t="str">
         <f>Calificacion!P$4</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AE2" s="103"/>
+      <c r="AE2" s="107"/>
     </row>
     <row r="3" spans="1:48" x14ac:dyDescent="0.45">
       <c r="B3" s="21" t="s">
@@ -7337,10 +7337,10 @@
       <c r="AE11" s="73"/>
     </row>
     <row r="12" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B12" s="106" t="s">
+      <c r="B12" s="111" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="106"/>
+      <c r="C12" s="111"/>
       <c r="D12" s="104">
         <f>AVERAGE(D4:D11)</f>
         <v>0</v>
@@ -7413,29 +7413,49 @@
       <c r="AE12" s="104"/>
     </row>
     <row r="13" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B13" s="108" t="s">
+      <c r="B13" s="109" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="108"/>
+      <c r="C13" s="109"/>
     </row>
     <row r="14" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B14" s="107"/>
-      <c r="C14" s="107"/>
+      <c r="B14" s="105"/>
+      <c r="C14" s="105"/>
     </row>
     <row r="15" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B15" s="107"/>
-      <c r="C15" s="107"/>
+      <c r="B15" s="105"/>
+      <c r="C15" s="105"/>
     </row>
     <row r="16" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="B16" s="107"/>
-      <c r="C16" s="107"/>
+      <c r="B16" s="105"/>
+      <c r="C16" s="105"/>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B17" s="107"/>
-      <c r="C17" s="107"/>
+      <c r="B17" s="105"/>
+      <c r="C17" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="Z12:AA12"/>
+    <mergeCell ref="AD12:AE12"/>
+    <mergeCell ref="AB12:AC12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="AD2:AE2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="AB2:AC2"/>
     <mergeCell ref="B13:C17"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:G2"/>
@@ -7446,26 +7466,6 @@
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="H12:I12"/>
     <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="AD2:AE2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="V2:W2"/>
-    <mergeCell ref="AB2:AC2"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="Z12:AA12"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="AB12:AC12"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
